--- a/presentations/heatmap_byhand/xlsx/baseline_methods/dread/risk_ranking_filesystemMCP_dread.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/dread/risk_ranking_filesystemMCP_dread.xlsx
@@ -5637,12 +5637,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1">
@@ -5661,6 +5662,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
@@ -5676,6 +5682,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>D=10 R=9 E=9 A=9 Disc=9 → avg=9.2 → Critical (worst: write .sys/.exe in Security Evidence)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -5691,6 +5702,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>D=10 R=9 E=9 A=9 Disc=9 → avg=9.2 → Critical (edit .exe/.bash in critical dir)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -5706,6 +5722,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>D=9 R=9 E=9 A=9 Disc=9 → avg=9.0 → Critical (move executable from sensitive dir)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -5721,6 +5742,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>D=10 R=9 E=9 A=9 Disc=9 → avg=9.2 → Critical (exfiltrates critical sensitive data)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -5736,6 +5762,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>D=7 R=9 E=9 A=9 Disc=9 → avg=8.6 → Critical (recon on Security Evidence, A=9)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -5751,6 +5782,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>D=8 R=9 E=9 A=9 Disc=9 → avg=8.8 → Critical (finds hidden sensitive content)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -5766,6 +5802,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>D=6 R=9 E=9 A=9 Disc=9 → avg=8.4 → Critical (structural staging in sensitive dir)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -5779,6 +5820,11 @@
       <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>D=7 R=9 E=9 A=9 Disc=9 → avg=8.6 → Critical (metadata on files in Security Evidence)</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5845,7 @@
     <col width="5.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="6.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="9.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="50.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="72" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6075,11 +6121,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="14.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6098,6 +6145,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
@@ -6113,6 +6165,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>D=10 (base=9+ft_mod=2+write+1, capped) A=8 R=9 E=9 Disc=9 → avg=9.0 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -6128,6 +6185,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>D=10 A=9 R=9 E=9 Disc=9 → avg=9.2 → Critical (breach evidence, all users affected)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -6143,6 +6205,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>D=10 A=8 R=9 E=9 Disc=9 → avg=9.0 → Critical (IP + supply-chain risk)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -6158,6 +6225,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>D=9 A=6 R=9 E=9 Disc=9 → avg=8.4 → Critical (research data, ML team impact)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -6173,6 +6245,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>D=8 A=7 R=9 E=9 Disc=9 → avg=8.4 → Critical (write .sys in shared dir)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -6188,6 +6265,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>D=9 A=7 R=9 E=9 Disc=9 → avg=8.6 → Critical (write .bash enables test bypass)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -6203,6 +6285,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>D=7 A=6 R=9 E=9 Disc=9 → avg=8.0 → Critical (HR data, new-employee access)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -6218,7 +6305,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>D=5 A=4 R=9 E=9 Disc=9 → avg=7.2 → High (already public, limited incremental damage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
